--- a/Examples/aatoCB8-g1_csc_extract.xlsx
+++ b/Examples/aatoCB8-g1_csc_extract.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -408,7 +408,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MicroJoules</t>
+          <t>Time (seconds)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -423,14 +423,14 @@
           <t>calUnitsColumnIndex</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -442,7 +442,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Time (seconds)</t>
+          <t>Raw Heat Rate (</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -459,17 +459,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Raw Heat Rate (J / s)</t>
+          <t>J / s)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>high</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Reconstructed from split tokens</t>
         </is>
       </c>
     </row>
@@ -632,14 +627,14 @@
           <t>Temperature</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -753,12 +748,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Matched with lookahead offset 2</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -819,14 +819,14 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Titration</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Likely empty in source</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -853,14 +853,14 @@
           <t>ContinousTitration</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Titration</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -904,14 +904,14 @@
           <t>PartiallyFilledCell</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -921,14 +921,14 @@
           <t>DefaultInjVolume</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -938,14 +938,14 @@
           <t>TotalContInjVolume</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -955,14 +955,14 @@
           <t>Version</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -972,14 +972,14 @@
           <t>ConstantSubtraction</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Not available in parsed value stream</t>
+          <t>Token did not match expected type</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,194 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ModelFitSettings</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bBaselineExists</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bValidAnalysisForBatch</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bValidExperimentParams</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>bFitClosenessCriteriaMet</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FitModels</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ConfidenceSettings</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NumModels</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ITCResultsLog</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ReportViews</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MicroJoules</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1281,10 @@
         <v>300</v>
       </c>
       <c r="C2">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D2">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="E2">
         <v>300</v>
@@ -1120,10 +1307,10 @@
         <v>500</v>
       </c>
       <c r="C3">
-        <v>623</v>
+        <v>700</v>
       </c>
       <c r="D3">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="E3">
         <v>500</v>
@@ -1146,10 +1333,10 @@
         <v>700</v>
       </c>
       <c r="C4">
-        <v>835</v>
+        <v>900</v>
       </c>
       <c r="D4">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="E4">
         <v>700</v>
@@ -1172,10 +1359,10 @@
         <v>900</v>
       </c>
       <c r="C5">
-        <v>1043</v>
+        <v>1100</v>
       </c>
       <c r="D5">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>900</v>
@@ -1198,10 +1385,10 @@
         <v>1100</v>
       </c>
       <c r="C6">
-        <v>1283</v>
+        <v>1300</v>
       </c>
       <c r="D6">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E6">
         <v>1100</v>
@@ -1224,10 +1411,10 @@
         <v>1300</v>
       </c>
       <c r="C7">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="D7">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E7">
         <v>1300</v>
@@ -1250,10 +1437,10 @@
         <v>1500</v>
       </c>
       <c r="C8">
-        <v>1607</v>
+        <v>1700</v>
       </c>
       <c r="D8">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="E8">
         <v>1500</v>
@@ -1276,10 +1463,10 @@
         <v>1700</v>
       </c>
       <c r="C9">
-        <v>1815</v>
+        <v>1900</v>
       </c>
       <c r="D9">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>1700</v>
@@ -1302,10 +1489,10 @@
         <v>1900</v>
       </c>
       <c r="C10">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10">
         <v>1900</v>
@@ -1328,10 +1515,10 @@
         <v>2100</v>
       </c>
       <c r="C11">
-        <v>2230</v>
+        <v>2300</v>
       </c>
       <c r="D11">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="E11">
         <v>2100</v>
@@ -1354,10 +1541,10 @@
         <v>2300</v>
       </c>
       <c r="C12">
-        <v>2418</v>
+        <v>2500</v>
       </c>
       <c r="D12">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="E12">
         <v>2300</v>
@@ -1380,10 +1567,10 @@
         <v>2500</v>
       </c>
       <c r="C13">
-        <v>2678</v>
+        <v>2700</v>
       </c>
       <c r="D13">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E13">
         <v>2500</v>
@@ -1406,10 +1593,10 @@
         <v>2700</v>
       </c>
       <c r="C14">
-        <v>2827</v>
+        <v>2900</v>
       </c>
       <c r="D14">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="E14">
         <v>2700</v>
@@ -1458,10 +1645,10 @@
         <v>3100</v>
       </c>
       <c r="C16">
-        <v>3198</v>
+        <v>3300</v>
       </c>
       <c r="D16">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="E16">
         <v>3100</v>
@@ -1484,10 +1671,10 @@
         <v>3300</v>
       </c>
       <c r="C17">
-        <v>3458</v>
+        <v>3500</v>
       </c>
       <c r="D17">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="E17">
         <v>3300</v>
@@ -1510,10 +1697,10 @@
         <v>3500</v>
       </c>
       <c r="C18">
-        <v>3602</v>
+        <v>3700</v>
       </c>
       <c r="D18">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="E18">
         <v>3500</v>
@@ -1536,10 +1723,10 @@
         <v>3700</v>
       </c>
       <c r="C19">
-        <v>3783</v>
+        <v>3900</v>
       </c>
       <c r="D19">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="E19">
         <v>3700</v>
@@ -1562,10 +1749,10 @@
         <v>3900</v>
       </c>
       <c r="C20">
-        <v>4057</v>
+        <v>4100</v>
       </c>
       <c r="D20">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="E20">
         <v>3900</v>
@@ -1588,10 +1775,10 @@
         <v>4100</v>
       </c>
       <c r="C21">
-        <v>4184</v>
+        <v>4300</v>
       </c>
       <c r="D21">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="E21">
         <v>4100</v>
